--- a/final_results/final_params_all_models_all_organs.xlsx
+++ b/final_results/final_params_all_models_all_organs.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kadyrova\Desktop\github_repos\medical-segmentation-calibration-ood\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkkad\Desktop\github_repos\medical-segmentation-calibration-ood\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46B599C-BDE1-4605-AB64-7469C6068DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F877D-1C6B-4C99-9E45-346946F96810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9B8CA0CB-CC03-4271-B8DF-F5749B3F5A21}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="3" xr2:uid="{9B8CA0CB-CC03-4271-B8DF-F5749B3F5A21}"/>
   </bookViews>
   <sheets>
     <sheet name="train" sheetId="1" r:id="rId1"/>
     <sheet name="validation" sheetId="2" r:id="rId2"/>
     <sheet name="test" sheetId="3" r:id="rId3"/>
-    <sheet name="inference" sheetId="4" r:id="rId4"/>
+    <sheet name="test_2_comparison" sheetId="5" r:id="rId4"/>
+    <sheet name="inference" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">train!$A$1:$K$28</definedName>
@@ -35,15 +36,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="63">
   <si>
     <t>Dataset</t>
   </si>
@@ -226,13 +224,19 @@
   </si>
   <si>
     <t>Test inference</t>
+  </si>
+  <si>
+    <t>KITS20</t>
+  </si>
+  <si>
+    <t>KITS21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +248,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -299,9 +309,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -309,6 +316,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -329,9 +339,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -369,7 +379,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -475,7 +485,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -617,7 +627,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -628,8 +638,8 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
@@ -685,10 +695,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="7"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -724,8 +734,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -761,8 +771,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -798,10 +808,10 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -839,8 +849,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -876,8 +886,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -913,10 +923,10 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -954,8 +964,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -991,8 +1001,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -1028,8 +1038,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -1067,8 +1077,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -1104,8 +1114,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -1141,8 +1151,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -1180,8 +1190,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -1217,8 +1227,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -1254,8 +1264,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -1293,8 +1303,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -1330,8 +1340,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -1367,8 +1377,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -1406,8 +1416,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -1443,8 +1453,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -1480,8 +1490,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -1519,8 +1529,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -1556,8 +1566,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -1593,10 +1603,10 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -1634,8 +1644,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -1671,8 +1681,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>
@@ -1715,17 +1725,17 @@
     <sortCondition ref="C2:C28"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A25"/>
     <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1737,8 +1747,8 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6" bestFit="1" customWidth="1"/>
@@ -1792,10 +1802,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="7"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -1831,8 +1841,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -1868,8 +1878,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -1905,10 +1915,10 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -1946,8 +1956,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -1983,8 +1993,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -2020,10 +2030,10 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -2061,8 +2071,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -2098,8 +2108,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -2135,8 +2145,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -2174,8 +2184,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -2211,8 +2221,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -2248,8 +2258,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -2287,8 +2297,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -2324,8 +2334,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -2361,8 +2371,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -2400,8 +2410,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -2437,8 +2447,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -2474,8 +2484,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -2513,8 +2523,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -2550,8 +2560,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -2587,8 +2597,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -2626,8 +2636,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -2663,8 +2673,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -2700,10 +2710,10 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -2741,8 +2751,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -2778,8 +2788,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>
@@ -2821,11 +2831,6 @@
     <sortCondition ref="C2:C28"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A8:A25"/>
     <mergeCell ref="A2:B4"/>
@@ -2833,6 +2838,11 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2843,8 +2853,8 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -2895,10 +2905,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="7"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -2931,8 +2941,8 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -2965,8 +2975,8 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -2999,10 +3009,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -3037,8 +3047,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -3071,8 +3081,8 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -3105,10 +3115,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -3143,8 +3153,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -3177,8 +3187,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -3211,8 +3221,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -3247,8 +3257,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -3281,8 +3291,8 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -3315,8 +3325,8 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -3351,8 +3361,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -3385,8 +3395,8 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -3419,8 +3429,8 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -3455,8 +3465,8 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -3489,8 +3499,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -3523,8 +3533,8 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -3559,8 +3569,8 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -3593,8 +3603,8 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -3627,8 +3637,8 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -3663,8 +3673,8 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -3697,8 +3707,8 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -3731,10 +3741,10 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -3769,8 +3779,8 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -3803,8 +3813,8 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>
@@ -3843,16 +3853,16 @@
     <sortCondition ref="C2:C28"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="A8:A25"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="B17:B19"/>
   </mergeCells>
@@ -3861,12 +3871,383 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{085B5E20-BABC-428E-80E7-13E9FDD054DD}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>77.37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2">
+        <v>70.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>81.52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>75.83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2">
+        <v>77.64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2">
+        <v>74.989999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2">
+        <v>97.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>99.63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <v>97.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2">
+        <v>99.87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2">
+        <v>95.74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="2">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2">
+        <v>99.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="2">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="2">
+        <v>99.74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2">
+        <v>99.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="2">
+        <v>77.790000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="2">
+        <v>78.319999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="2">
+        <v>61.69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="2">
+        <v>81.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="2">
+        <v>77.77</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D25">
+    <sortCondition ref="C2:C25"/>
+    <sortCondition ref="B2:B25"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CD88816-FAD1-4D98-B463-2E65209B33D8}">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
@@ -3894,10 +4275,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="7"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -3912,8 +4293,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -3928,8 +4309,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -3944,10 +4325,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -3964,8 +4345,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -3980,8 +4361,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -3996,10 +4377,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -4016,8 +4397,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -4032,8 +4413,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -4048,8 +4429,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -4066,8 +4447,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -4082,8 +4463,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -4098,8 +4479,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -4116,8 +4497,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -4132,8 +4513,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -4148,8 +4529,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -4166,8 +4547,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -4182,8 +4563,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -4198,8 +4579,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -4216,8 +4597,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -4232,8 +4613,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -4248,8 +4629,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -4266,8 +4647,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -4282,8 +4663,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -4298,10 +4679,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -4318,8 +4699,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -4334,8 +4715,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>

--- a/final_results/final_params_all_models_all_organs.xlsx
+++ b/final_results/final_params_all_models_all_organs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkkad\Desktop\github_repos\medical-segmentation-calibration-ood\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkkad\Desktop\github_repos\medical-segmentation-calibration-ood\final_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F877D-1C6B-4C99-9E45-346946F96810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5369BEFF-AD2F-4C6F-A741-42649292EEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="3" xr2:uid="{9B8CA0CB-CC03-4271-B8DF-F5749B3F5A21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="5" xr2:uid="{9B8CA0CB-CC03-4271-B8DF-F5749B3F5A21}"/>
   </bookViews>
   <sheets>
     <sheet name="train" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,12 @@
     <sheet name="test" sheetId="3" r:id="rId3"/>
     <sheet name="test_2_comparison" sheetId="5" r:id="rId4"/>
     <sheet name="inference" sheetId="4" r:id="rId5"/>
+    <sheet name="single vs multitask" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">train!$A$1:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">test!$A$1:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">train!$A$1:$M$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">validation!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="75">
   <si>
     <t>Dataset</t>
   </si>
@@ -230,13 +233,49 @@
   </si>
   <si>
     <t>KITS21</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>DCS (Multi-task learning)</t>
+  </si>
+  <si>
+    <t>Project replicated model</t>
+  </si>
+  <si>
+    <t>Validation test</t>
+  </si>
+  <si>
+    <t>hippocampus</t>
+  </si>
+  <si>
+    <t>DSC (Single-task learning)</t>
+  </si>
+  <si>
+    <t>Project model</t>
+  </si>
+  <si>
+    <t>DSC (Multi-single difference)</t>
+  </si>
+  <si>
+    <t>Single-task</t>
+  </si>
+  <si>
+    <t>Multi-task</t>
+  </si>
+  <si>
+    <t>Dice Score Coefficient (test)</t>
+  </si>
+  <si>
+    <t>Dice Score Coefficient diff for test only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +294,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -264,7 +324,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -296,11 +356,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -315,17 +404,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -635,6 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC147C0-D021-4104-9920-DFD0276F5DED}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -694,11 +909,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="11"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -733,9 +948,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -771,8 +986,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -807,11 +1022,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -848,9 +1063,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -886,8 +1101,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -922,11 +1137,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -963,9 +1178,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -1001,8 +1216,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -1037,9 +1252,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -1076,9 +1291,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -1114,8 +1329,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -1150,9 +1365,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -1189,9 +1404,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -1227,8 +1442,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -1263,9 +1478,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -1302,9 +1517,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -1340,8 +1555,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -1376,9 +1591,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -1415,9 +1630,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -1453,8 +1668,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -1489,9 +1704,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -1528,9 +1743,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -1566,8 +1781,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -1602,11 +1817,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -1643,9 +1858,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -1681,8 +1896,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>
@@ -1718,7 +1933,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K28" xr:uid="{4EC147C0-D021-4104-9920-DFD0276F5DED}"/>
+  <autoFilter ref="A1:M28" xr:uid="{4EC147C0-D021-4104-9920-DFD0276F5DED}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="SegResNet"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M28">
     <sortCondition ref="A2:A28"/>
     <sortCondition ref="B2:B28"/>
@@ -1738,12 +1959,29 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="B17:B19"/>
   </mergeCells>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="top10" dxfId="12" priority="6" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="top10" dxfId="11" priority="4" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:J1048576">
+    <cfRule type="top10" dxfId="10" priority="5" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="top10" dxfId="9" priority="2" rank="1"/>
+    <cfRule type="top10" priority="3" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="top10" dxfId="8" priority="1" rank="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5374FD21-0F68-466F-B0E5-E7F60551CEDF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1801,11 +2039,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -1840,9 +2080,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -1877,9 +2121,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -1914,807 +2162,873 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2">
-        <v>60.51</v>
+        <v>66.27</v>
       </c>
       <c r="F5" s="2">
-        <v>71.790000000000006</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="G5" s="2">
-        <v>74.06</v>
+        <v>83.02</v>
       </c>
       <c r="H5" s="2">
-        <v>73.31</v>
+        <v>83.11</v>
       </c>
       <c r="I5" s="2">
-        <v>74.06</v>
+        <v>83.02</v>
       </c>
       <c r="J5" s="2">
-        <v>72.22</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="K5" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2">
-        <v>90.14</v>
+        <v>93.84</v>
       </c>
       <c r="F6" s="2">
-        <v>94.59</v>
+        <v>96.71</v>
       </c>
       <c r="G6" s="2">
-        <v>94.84</v>
+        <v>97.08</v>
       </c>
       <c r="H6" s="2">
-        <v>94.37</v>
+        <v>96.4</v>
       </c>
       <c r="I6" s="2">
-        <v>94.84</v>
+        <v>97.08</v>
       </c>
       <c r="J6" s="2">
-        <v>95.15</v>
+        <v>97.04</v>
       </c>
       <c r="K6" s="2">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2">
-        <v>67.48</v>
+        <v>66.790000000000006</v>
       </c>
       <c r="F7" s="2">
-        <v>78.489999999999995</v>
+        <v>77.89</v>
       </c>
       <c r="G7" s="2">
-        <v>83.4</v>
+        <v>83.04</v>
       </c>
       <c r="H7" s="2">
-        <v>82.74</v>
+        <v>82.66</v>
       </c>
       <c r="I7" s="2">
-        <v>83.4</v>
+        <v>83.04</v>
       </c>
       <c r="J7" s="2">
-        <v>78.510000000000005</v>
+        <v>77.89</v>
       </c>
       <c r="K7" s="2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>12</v>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2">
-        <v>66.27</v>
+        <v>59.52</v>
       </c>
       <c r="F8" s="2">
-        <v>77.430000000000007</v>
+        <v>70.14</v>
       </c>
       <c r="G8" s="2">
-        <v>83.02</v>
+        <v>70.290000000000006</v>
       </c>
       <c r="H8" s="2">
-        <v>83.11</v>
+        <v>70.11</v>
       </c>
       <c r="I8" s="2">
-        <v>83.02</v>
+        <v>70.290000000000006</v>
       </c>
       <c r="J8" s="2">
-        <v>77.430000000000007</v>
+        <v>72.709999999999994</v>
       </c>
       <c r="K8" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="L8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2">
-        <v>93.84</v>
+        <v>99.29</v>
       </c>
       <c r="F9" s="2">
-        <v>96.71</v>
+        <v>99.64</v>
       </c>
       <c r="G9" s="2">
-        <v>97.08</v>
+        <v>99.64</v>
       </c>
       <c r="H9" s="2">
-        <v>96.4</v>
+        <v>99.64</v>
       </c>
       <c r="I9" s="2">
-        <v>97.08</v>
+        <v>99.64</v>
       </c>
       <c r="J9" s="2">
-        <v>97.04</v>
+        <v>99.68</v>
       </c>
       <c r="K9" s="2">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="E10" s="2">
-        <v>66.790000000000006</v>
+        <v>99.67</v>
       </c>
       <c r="F10" s="2">
-        <v>77.89</v>
+        <v>99.83</v>
       </c>
       <c r="G10" s="2">
-        <v>83.04</v>
+        <v>99.81</v>
       </c>
       <c r="H10" s="2">
-        <v>82.66</v>
+        <v>99.85</v>
       </c>
       <c r="I10" s="2">
-        <v>83.04</v>
+        <v>99.81</v>
       </c>
       <c r="J10" s="2">
-        <v>77.89</v>
+        <v>99.85</v>
       </c>
       <c r="K10" s="2">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="L10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
-        <v>14</v>
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2">
-        <v>59.52</v>
+        <v>73.59</v>
       </c>
       <c r="F11" s="2">
-        <v>70.14</v>
+        <v>82.99</v>
       </c>
       <c r="G11" s="2">
-        <v>70.290000000000006</v>
+        <v>83.19</v>
       </c>
       <c r="H11" s="2">
-        <v>70.11</v>
+        <v>82.82</v>
       </c>
       <c r="I11" s="2">
-        <v>70.290000000000006</v>
+        <v>83.19</v>
       </c>
       <c r="J11" s="2">
-        <v>72.709999999999994</v>
+        <v>84.7</v>
       </c>
       <c r="K11" s="2">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="L11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2">
-        <v>99.29</v>
+        <v>95.97</v>
       </c>
       <c r="F12" s="2">
-        <v>99.64</v>
+        <v>97.88</v>
       </c>
       <c r="G12" s="2">
-        <v>99.64</v>
+        <v>97.82</v>
       </c>
       <c r="H12" s="2">
-        <v>99.64</v>
+        <v>97.96</v>
       </c>
       <c r="I12" s="2">
-        <v>99.64</v>
+        <v>97.82</v>
       </c>
       <c r="J12" s="2">
-        <v>99.68</v>
+        <v>98.13</v>
       </c>
       <c r="K12" s="2">
         <v>2.19</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="D13">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="E13" s="2">
-        <v>99.67</v>
+        <v>99.22</v>
       </c>
       <c r="F13" s="2">
-        <v>99.83</v>
+        <v>99.6</v>
       </c>
       <c r="G13" s="2">
-        <v>99.81</v>
+        <v>99.63</v>
       </c>
       <c r="H13" s="2">
-        <v>99.85</v>
+        <v>99.58</v>
       </c>
       <c r="I13" s="2">
-        <v>99.81</v>
+        <v>99.63</v>
       </c>
       <c r="J13" s="2">
-        <v>99.85</v>
+        <v>99.65</v>
       </c>
       <c r="K13" s="2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2">
-        <v>73.59</v>
+        <v>64.540000000000006</v>
       </c>
       <c r="F14" s="2">
-        <v>82.99</v>
+        <v>75.84</v>
       </c>
       <c r="G14" s="2">
-        <v>83.19</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="H14" s="2">
-        <v>82.82</v>
+        <v>79.89</v>
       </c>
       <c r="I14" s="2">
-        <v>83.19</v>
+        <v>80.430000000000007</v>
       </c>
       <c r="J14" s="2">
-        <v>84.7</v>
+        <v>75.86</v>
       </c>
       <c r="K14" s="2">
-        <v>0.66</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2">
-        <v>95.97</v>
+        <v>99.74</v>
       </c>
       <c r="F15" s="2">
-        <v>97.88</v>
+        <v>99.87</v>
       </c>
       <c r="G15" s="2">
-        <v>97.82</v>
+        <v>99.88</v>
       </c>
       <c r="H15" s="2">
-        <v>97.96</v>
+        <v>99.86</v>
       </c>
       <c r="I15" s="2">
-        <v>97.82</v>
+        <v>99.88</v>
       </c>
       <c r="J15" s="2">
-        <v>98.13</v>
+        <v>99.88</v>
       </c>
       <c r="K15" s="2">
-        <v>2.19</v>
+        <v>0.47</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C16" t="s">
         <v>40</v>
       </c>
       <c r="D16">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2">
-        <v>99.22</v>
+        <v>66.680000000000007</v>
       </c>
       <c r="F16" s="2">
-        <v>99.6</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="G16" s="2">
-        <v>99.63</v>
+        <v>83.34</v>
       </c>
       <c r="H16" s="2">
-        <v>99.58</v>
+        <v>83.33</v>
       </c>
       <c r="I16" s="2">
-        <v>99.63</v>
+        <v>83.34</v>
       </c>
       <c r="J16" s="2">
-        <v>99.65</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="K16" s="2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
-        <v>18</v>
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2">
-        <v>64.540000000000006</v>
+        <v>60.51</v>
       </c>
       <c r="F17" s="2">
-        <v>75.84</v>
+        <v>71.790000000000006</v>
       </c>
       <c r="G17" s="2">
-        <v>80.430000000000007</v>
+        <v>74.06</v>
       </c>
       <c r="H17" s="2">
-        <v>79.89</v>
+        <v>73.31</v>
       </c>
       <c r="I17" s="2">
-        <v>80.430000000000007</v>
+        <v>74.06</v>
       </c>
       <c r="J17" s="2">
-        <v>75.86</v>
+        <v>72.22</v>
       </c>
       <c r="K17" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2">
-        <v>99.74</v>
+        <v>90.14</v>
       </c>
       <c r="F18" s="2">
-        <v>99.87</v>
+        <v>94.59</v>
       </c>
       <c r="G18" s="2">
-        <v>99.88</v>
+        <v>94.84</v>
       </c>
       <c r="H18" s="2">
-        <v>99.86</v>
+        <v>94.37</v>
       </c>
       <c r="I18" s="2">
-        <v>99.88</v>
+        <v>94.84</v>
       </c>
       <c r="J18" s="2">
-        <v>99.88</v>
+        <v>95.15</v>
       </c>
       <c r="K18" s="2">
-        <v>0.47</v>
+        <v>2.19</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M18" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2">
-        <v>66.680000000000007</v>
+        <v>67.48</v>
       </c>
       <c r="F19" s="2">
-        <v>77.790000000000006</v>
+        <v>78.489999999999995</v>
       </c>
       <c r="G19" s="2">
-        <v>83.34</v>
+        <v>83.4</v>
       </c>
       <c r="H19" s="2">
-        <v>83.33</v>
+        <v>82.74</v>
       </c>
       <c r="I19" s="2">
-        <v>83.34</v>
+        <v>83.4</v>
       </c>
       <c r="J19" s="2">
-        <v>77.790000000000006</v>
+        <v>78.510000000000005</v>
       </c>
       <c r="K19" s="2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="L19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
-        <v>26</v>
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2">
-        <v>66.56</v>
+        <v>59.1</v>
       </c>
       <c r="F20" s="2">
-        <v>77.680000000000007</v>
+        <v>69.63</v>
       </c>
       <c r="G20" s="2">
-        <v>83.24</v>
+        <v>69.73</v>
       </c>
       <c r="H20" s="2">
-        <v>83.27</v>
+        <v>69.61</v>
       </c>
       <c r="I20" s="2">
-        <v>83.24</v>
+        <v>69.73</v>
       </c>
       <c r="J20" s="2">
-        <v>77.680000000000007</v>
+        <v>72.42</v>
       </c>
       <c r="K20" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2">
-        <v>99.92</v>
+        <v>99.19</v>
       </c>
       <c r="F21" s="2">
-        <v>99.96</v>
+        <v>99.59</v>
       </c>
       <c r="G21" s="2">
-        <v>99.96</v>
+        <v>99.6</v>
       </c>
       <c r="H21" s="2">
-        <v>99.96</v>
+        <v>99.58</v>
       </c>
       <c r="I21" s="2">
-        <v>99.96</v>
+        <v>99.6</v>
       </c>
       <c r="J21" s="2">
-        <v>99.96</v>
+        <v>99.64</v>
       </c>
       <c r="K21" s="2">
         <v>0.47</v>
       </c>
       <c r="L21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2">
-        <v>71.239999999999995</v>
+        <v>56.28</v>
       </c>
       <c r="F22" s="2">
-        <v>81.62</v>
+        <v>61.46</v>
       </c>
       <c r="G22" s="2">
-        <v>85.49</v>
+        <v>67.12</v>
       </c>
       <c r="H22" s="2">
-        <v>83.77</v>
+        <v>74.33</v>
       </c>
       <c r="I22" s="2">
-        <v>85.49</v>
+        <v>67.12</v>
       </c>
       <c r="J22" s="2">
-        <v>81.790000000000006</v>
+        <v>77.87</v>
       </c>
       <c r="K22" s="2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="L22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
-        <v>28</v>
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="E23" s="2">
-        <v>64.430000000000007</v>
+        <v>66.56</v>
       </c>
       <c r="F23" s="2">
-        <v>74.989999999999995</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="G23" s="2">
-        <v>74.989999999999995</v>
+        <v>83.24</v>
       </c>
       <c r="H23" s="2">
-        <v>74.989999999999995</v>
+        <v>83.27</v>
       </c>
       <c r="I23" s="2">
-        <v>74.989999999999995</v>
+        <v>83.24</v>
       </c>
       <c r="J23" s="2">
-        <v>77.77</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="K23" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
-        <v>99.7</v>
+        <v>99.92</v>
       </c>
       <c r="F24" s="2">
-        <v>99.85</v>
+        <v>99.96</v>
       </c>
       <c r="G24" s="2">
-        <v>99.85</v>
+        <v>99.96</v>
       </c>
       <c r="H24" s="2">
-        <v>99.85</v>
+        <v>99.96</v>
       </c>
       <c r="I24" s="2">
-        <v>99.85</v>
+        <v>99.96</v>
       </c>
       <c r="J24" s="2">
-        <v>99.86</v>
+        <v>99.96</v>
       </c>
       <c r="K24" s="2">
         <v>0.47</v>
       </c>
       <c r="L24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M24" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2">
-        <v>66.650000000000006</v>
+        <v>71.239999999999995</v>
       </c>
       <c r="F25" s="2">
-        <v>77.760000000000005</v>
+        <v>81.62</v>
       </c>
       <c r="G25" s="2">
-        <v>83.29</v>
+        <v>85.49</v>
       </c>
       <c r="H25" s="2">
-        <v>83.26</v>
+        <v>83.77</v>
       </c>
       <c r="I25" s="2">
-        <v>83.29</v>
+        <v>85.49</v>
       </c>
       <c r="J25" s="2">
-        <v>77.760000000000005</v>
+        <v>81.790000000000006</v>
       </c>
       <c r="K25" s="2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M25" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
@@ -2723,133 +3037,152 @@
         <v>26</v>
       </c>
       <c r="E26" s="2">
-        <v>59.1</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="F26" s="2">
-        <v>69.63</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="G26" s="2">
-        <v>69.73</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="H26" s="2">
-        <v>69.61</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="I26" s="2">
-        <v>69.73</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="J26" s="2">
-        <v>72.42</v>
+        <v>77.77</v>
       </c>
       <c r="K26" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M26" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="E27" s="2">
-        <v>99.19</v>
+        <v>99.7</v>
       </c>
       <c r="F27" s="2">
-        <v>99.59</v>
+        <v>99.85</v>
       </c>
       <c r="G27" s="2">
-        <v>99.6</v>
+        <v>99.85</v>
       </c>
       <c r="H27" s="2">
-        <v>99.58</v>
+        <v>99.85</v>
       </c>
       <c r="I27" s="2">
-        <v>99.6</v>
+        <v>99.85</v>
       </c>
       <c r="J27" s="2">
-        <v>99.64</v>
+        <v>99.86</v>
       </c>
       <c r="K27" s="2">
         <v>0.47</v>
       </c>
       <c r="L27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E28" s="2">
-        <v>56.28</v>
+        <v>66.650000000000006</v>
       </c>
       <c r="F28" s="2">
-        <v>61.46</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="G28" s="2">
-        <v>67.12</v>
+        <v>83.29</v>
       </c>
       <c r="H28" s="2">
-        <v>74.33</v>
+        <v>83.26</v>
       </c>
       <c r="I28" s="2">
-        <v>67.12</v>
+        <v>83.29</v>
       </c>
       <c r="J28" s="2">
-        <v>77.87</v>
+        <v>77.760000000000005</v>
       </c>
       <c r="K28" s="2">
         <v>1.63</v>
       </c>
       <c r="L28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M28" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M28" xr:uid="{5374FD21-0F68-466F-B0E5-E7F60551CEDF}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="KITS19"/>
+        <filter val="MSD"/>
+        <filter val="SLIVER"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="SegResNet"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:M28">
+      <sortCondition ref="B1:B28"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M28">
     <sortCondition ref="A2:A28"/>
     <sortCondition ref="B2:B28"/>
     <sortCondition ref="C2:C28"/>
   </sortState>
-  <mergeCells count="12">
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A8:A25"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="top10" dxfId="7" priority="1" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:J1048576">
+    <cfRule type="top10" dxfId="6" priority="2" rank="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30144AD4-F371-48B7-B81D-C1548C034AB9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2904,11 +3237,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -2940,9 +3275,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -2974,9 +3313,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -3008,864 +3351,960 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>21</v>
+    <row r="5" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2">
-        <v>60.21</v>
+        <v>66.209999999999994</v>
       </c>
       <c r="E5" s="2">
-        <v>71.5</v>
+        <v>77.37</v>
       </c>
       <c r="F5" s="2">
-        <v>73.67</v>
+        <v>82.98</v>
       </c>
       <c r="G5" s="2">
-        <v>57.91</v>
+        <v>66.05</v>
       </c>
       <c r="H5" s="2">
-        <v>73.67</v>
+        <v>82.98</v>
       </c>
       <c r="I5" s="2">
-        <v>71.94</v>
+        <v>77.37</v>
       </c>
       <c r="J5" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="K5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+    <row r="6" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="E6" s="2">
-        <v>95.74</v>
+        <v>97.21</v>
       </c>
       <c r="F6" s="2">
-        <v>95.85</v>
+        <v>97.54</v>
       </c>
       <c r="G6" s="2">
-        <v>94.31</v>
+        <v>96.23</v>
       </c>
       <c r="H6" s="2">
-        <v>95.85</v>
+        <v>97.54</v>
       </c>
       <c r="I6" s="2">
-        <v>96.2</v>
+        <v>97.49</v>
       </c>
       <c r="J6" s="2">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="2">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="E7" s="2">
-        <v>78.319999999999993</v>
+        <v>77.8</v>
       </c>
       <c r="F7" s="2">
-        <v>83.32</v>
+        <v>83.01</v>
       </c>
       <c r="G7" s="2">
-        <v>67.510000000000005</v>
+        <v>66.709999999999994</v>
       </c>
       <c r="H7" s="2">
-        <v>83.32</v>
+        <v>83.01</v>
       </c>
       <c r="I7" s="2">
-        <v>78.34</v>
+        <v>77.81</v>
       </c>
       <c r="J7" s="2">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>12</v>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2">
-        <v>66.209999999999994</v>
+        <v>59.53</v>
       </c>
       <c r="E8" s="2">
-        <v>77.37</v>
+        <v>70.16</v>
       </c>
       <c r="F8" s="2">
-        <v>82.98</v>
+        <v>70.33</v>
       </c>
       <c r="G8" s="2">
-        <v>66.05</v>
+        <v>59.04</v>
       </c>
       <c r="H8" s="2">
-        <v>82.98</v>
+        <v>70.33</v>
       </c>
       <c r="I8" s="2">
-        <v>77.37</v>
+        <v>72.69</v>
       </c>
       <c r="J8" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L8" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+    <row r="9" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="2">
-        <v>94.73</v>
+        <v>99.26</v>
       </c>
       <c r="E9" s="2">
-        <v>97.21</v>
+        <v>99.63</v>
       </c>
       <c r="F9" s="2">
-        <v>97.54</v>
+        <v>99.63</v>
       </c>
       <c r="G9" s="2">
-        <v>96.23</v>
+        <v>99.51</v>
       </c>
       <c r="H9" s="2">
-        <v>97.54</v>
+        <v>99.63</v>
       </c>
       <c r="I9" s="2">
-        <v>97.49</v>
+        <v>99.67</v>
       </c>
       <c r="J9" s="2">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="2">
-        <v>66.7</v>
+        <v>99.48</v>
       </c>
       <c r="E10" s="2">
-        <v>77.8</v>
+        <v>99.74</v>
       </c>
       <c r="F10" s="2">
-        <v>83.01</v>
+        <v>99.7</v>
       </c>
       <c r="G10" s="2">
-        <v>66.709999999999994</v>
+        <v>99.65</v>
       </c>
       <c r="H10" s="2">
-        <v>83.01</v>
+        <v>99.7</v>
       </c>
       <c r="I10" s="2">
-        <v>77.81</v>
+        <v>99.77</v>
       </c>
       <c r="J10" s="2">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
-        <v>14</v>
+    <row r="11" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="2">
-        <v>59.53</v>
+        <v>71.86</v>
       </c>
       <c r="E11" s="2">
-        <v>70.16</v>
+        <v>81.52</v>
       </c>
       <c r="F11" s="2">
-        <v>70.33</v>
+        <v>81.7</v>
       </c>
       <c r="G11" s="2">
-        <v>59.04</v>
+        <v>75.08</v>
       </c>
       <c r="H11" s="2">
-        <v>70.33</v>
+        <v>81.7</v>
       </c>
       <c r="I11" s="2">
-        <v>72.69</v>
+        <v>83.38</v>
       </c>
       <c r="J11" s="2">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+    <row r="12" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="C12" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="2">
-        <v>99.26</v>
+        <v>96.11</v>
       </c>
       <c r="E12" s="2">
-        <v>99.63</v>
+        <v>97.98</v>
       </c>
       <c r="F12" s="2">
-        <v>99.63</v>
+        <v>97.91</v>
       </c>
       <c r="G12" s="2">
-        <v>99.51</v>
+        <v>97.31</v>
       </c>
       <c r="H12" s="2">
-        <v>99.63</v>
+        <v>97.91</v>
       </c>
       <c r="I12" s="2">
-        <v>99.67</v>
+        <v>98.21</v>
       </c>
       <c r="J12" s="2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="2">
-        <v>99.48</v>
+        <v>99.26</v>
       </c>
       <c r="E13" s="2">
-        <v>99.74</v>
+        <v>99.63</v>
       </c>
       <c r="F13" s="2">
-        <v>99.7</v>
+        <v>99.65</v>
       </c>
       <c r="G13" s="2">
+        <v>99.5</v>
+      </c>
+      <c r="H13" s="2">
         <v>99.65</v>
       </c>
-      <c r="H13" s="2">
-        <v>99.7</v>
-      </c>
       <c r="I13" s="2">
-        <v>99.77</v>
+        <v>99.67</v>
       </c>
       <c r="J13" s="2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L13" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
-        <v>16</v>
+    <row r="14" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2">
-        <v>71.86</v>
+        <v>64.53</v>
       </c>
       <c r="E14" s="2">
-        <v>81.52</v>
+        <v>75.83</v>
       </c>
       <c r="F14" s="2">
-        <v>81.7</v>
+        <v>80.42</v>
       </c>
       <c r="G14" s="2">
-        <v>75.08</v>
+        <v>63.78</v>
       </c>
       <c r="H14" s="2">
-        <v>81.7</v>
+        <v>80.42</v>
       </c>
       <c r="I14" s="2">
-        <v>83.38</v>
+        <v>75.86</v>
       </c>
       <c r="J14" s="2">
-        <v>0.5</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+    <row r="15" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="2">
-        <v>96.11</v>
+        <v>99.74</v>
       </c>
       <c r="E15" s="2">
-        <v>97.98</v>
+        <v>99.87</v>
       </c>
       <c r="F15" s="2">
-        <v>97.91</v>
+        <v>99.88</v>
       </c>
       <c r="G15" s="2">
-        <v>97.31</v>
+        <v>99.82</v>
       </c>
       <c r="H15" s="2">
-        <v>97.91</v>
+        <v>99.88</v>
       </c>
       <c r="I15" s="2">
-        <v>98.21</v>
+        <v>99.88</v>
       </c>
       <c r="J15" s="2">
-        <v>1.97</v>
+        <v>0.48</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C16" t="s">
         <v>40</v>
       </c>
       <c r="D16" s="2">
-        <v>99.26</v>
+        <v>66.680000000000007</v>
       </c>
       <c r="E16" s="2">
-        <v>99.63</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="F16" s="2">
-        <v>99.65</v>
+        <v>83.34</v>
       </c>
       <c r="G16" s="2">
-        <v>99.5</v>
+        <v>66.680000000000007</v>
       </c>
       <c r="H16" s="2">
-        <v>99.65</v>
+        <v>83.34</v>
       </c>
       <c r="I16" s="2">
-        <v>99.67</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="J16" s="2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="K16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
-        <v>18</v>
+    <row r="17" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="2">
-        <v>64.53</v>
+        <v>60.21</v>
       </c>
       <c r="E17" s="2">
-        <v>75.83</v>
+        <v>71.5</v>
       </c>
       <c r="F17" s="2">
-        <v>80.42</v>
+        <v>73.67</v>
       </c>
       <c r="G17" s="2">
-        <v>63.78</v>
+        <v>57.91</v>
       </c>
       <c r="H17" s="2">
-        <v>80.42</v>
+        <v>73.67</v>
       </c>
       <c r="I17" s="2">
-        <v>75.86</v>
+        <v>71.94</v>
       </c>
       <c r="J17" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+    <row r="18" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C18" t="s">
         <v>30</v>
       </c>
       <c r="D18" s="2">
-        <v>99.74</v>
+        <v>92.17</v>
       </c>
       <c r="E18" s="2">
-        <v>99.87</v>
+        <v>95.74</v>
       </c>
       <c r="F18" s="2">
-        <v>99.88</v>
+        <v>95.85</v>
       </c>
       <c r="G18" s="2">
-        <v>99.82</v>
+        <v>94.31</v>
       </c>
       <c r="H18" s="2">
-        <v>99.88</v>
+        <v>95.85</v>
       </c>
       <c r="I18" s="2">
-        <v>99.88</v>
+        <v>96.2</v>
       </c>
       <c r="J18" s="2">
-        <v>0.48</v>
+        <v>1.96</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C19" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="2">
-        <v>66.680000000000007</v>
+        <v>67.3</v>
       </c>
       <c r="E19" s="2">
-        <v>77.790000000000006</v>
+        <v>78.319999999999993</v>
       </c>
       <c r="F19" s="2">
-        <v>83.34</v>
+        <v>83.32</v>
       </c>
       <c r="G19" s="2">
-        <v>66.680000000000007</v>
+        <v>67.510000000000005</v>
       </c>
       <c r="H19" s="2">
-        <v>83.34</v>
+        <v>83.32</v>
       </c>
       <c r="I19" s="2">
-        <v>77.790000000000006</v>
+        <v>78.34</v>
       </c>
       <c r="J19" s="2">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
-        <v>26</v>
+    <row r="20" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2">
-        <v>66.510000000000005</v>
+        <v>59.25</v>
       </c>
       <c r="E20" s="2">
-        <v>77.64</v>
+        <v>69.8</v>
       </c>
       <c r="F20" s="2">
-        <v>83.2</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="G20" s="2">
-        <v>66.459999999999994</v>
+        <v>58.81</v>
       </c>
       <c r="H20" s="2">
-        <v>83.2</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="I20" s="2">
-        <v>77.64</v>
+        <v>72.540000000000006</v>
       </c>
       <c r="J20" s="2">
         <v>0.14000000000000001</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+    <row r="21" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C21" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="2">
-        <v>99.78</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2">
-        <v>99.89</v>
+        <v>99.5</v>
       </c>
       <c r="F21" s="2">
-        <v>99.89</v>
+        <v>99.51</v>
       </c>
       <c r="G21" s="2">
-        <v>99.85</v>
+        <v>99.33</v>
       </c>
       <c r="H21" s="2">
-        <v>99.89</v>
+        <v>99.51</v>
       </c>
       <c r="I21" s="2">
-        <v>99.9</v>
+        <v>99.55</v>
       </c>
       <c r="J21" s="2">
         <v>0.48</v>
       </c>
       <c r="K21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L21" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C22" t="s">
         <v>40</v>
       </c>
       <c r="D22" s="2">
-        <v>71.64</v>
+        <v>56.43</v>
       </c>
       <c r="E22" s="2">
-        <v>81.94</v>
+        <v>61.69</v>
       </c>
       <c r="F22" s="2">
-        <v>85.76</v>
+        <v>67.27</v>
       </c>
       <c r="G22" s="2">
-        <v>73.17</v>
+        <v>66.989999999999995</v>
       </c>
       <c r="H22" s="2">
-        <v>85.76</v>
+        <v>67.27</v>
       </c>
       <c r="I22" s="2">
-        <v>82.11</v>
+        <v>78</v>
       </c>
       <c r="J22" s="2">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="K22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
-        <v>28</v>
+    <row r="23" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2">
-        <v>64.430000000000007</v>
+        <v>66.510000000000005</v>
       </c>
       <c r="E23" s="2">
-        <v>74.989999999999995</v>
+        <v>77.64</v>
       </c>
       <c r="F23" s="2">
-        <v>74.989999999999995</v>
+        <v>83.2</v>
       </c>
       <c r="G23" s="2">
-        <v>66.650000000000006</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="H23" s="2">
-        <v>74.989999999999995</v>
+        <v>83.2</v>
       </c>
       <c r="I23" s="2">
-        <v>77.77</v>
+        <v>77.64</v>
       </c>
       <c r="J23" s="2">
-        <v>0.13</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+    <row r="24" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="2">
-        <v>99.73</v>
+        <v>99.78</v>
       </c>
       <c r="E24" s="2">
-        <v>99.86</v>
+        <v>99.89</v>
       </c>
       <c r="F24" s="2">
-        <v>99.86</v>
+        <v>99.89</v>
       </c>
       <c r="G24" s="2">
-        <v>99.82</v>
+        <v>99.85</v>
       </c>
       <c r="H24" s="2">
-        <v>99.86</v>
+        <v>99.89</v>
       </c>
       <c r="I24" s="2">
-        <v>99.88</v>
+        <v>99.9</v>
       </c>
       <c r="J24" s="2">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="C25" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="2">
-        <v>66.650000000000006</v>
+        <v>71.64</v>
       </c>
       <c r="E25" s="2">
-        <v>77.77</v>
+        <v>81.94</v>
       </c>
       <c r="F25" s="2">
-        <v>83.29</v>
+        <v>85.76</v>
       </c>
       <c r="G25" s="2">
-        <v>66.650000000000006</v>
+        <v>73.17</v>
       </c>
       <c r="H25" s="2">
-        <v>83.29</v>
+        <v>85.76</v>
       </c>
       <c r="I25" s="2">
-        <v>77.77</v>
+        <v>82.11</v>
       </c>
       <c r="J25" s="2">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="K25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>24</v>
+    <row r="26" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2">
-        <v>59.25</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="E26" s="2">
-        <v>69.8</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="F26" s="2">
-        <v>69.900000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="G26" s="2">
-        <v>58.81</v>
+        <v>66.650000000000006</v>
       </c>
       <c r="H26" s="2">
-        <v>69.900000000000006</v>
+        <v>74.989999999999995</v>
       </c>
       <c r="I26" s="2">
-        <v>72.540000000000006</v>
+        <v>77.77</v>
       </c>
       <c r="J26" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+    <row r="27" spans="1:12" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="C27" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="2">
-        <v>99</v>
+        <v>99.73</v>
       </c>
       <c r="E27" s="2">
-        <v>99.5</v>
+        <v>99.86</v>
       </c>
       <c r="F27" s="2">
-        <v>99.51</v>
+        <v>99.86</v>
       </c>
       <c r="G27" s="2">
-        <v>99.33</v>
+        <v>99.82</v>
       </c>
       <c r="H27" s="2">
-        <v>99.51</v>
+        <v>99.86</v>
       </c>
       <c r="I27" s="2">
-        <v>99.55</v>
+        <v>99.88</v>
       </c>
       <c r="J27" s="2">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="K27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L27" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="2">
-        <v>56.43</v>
+        <v>66.650000000000006</v>
       </c>
       <c r="E28" s="2">
-        <v>61.69</v>
+        <v>77.77</v>
       </c>
       <c r="F28" s="2">
-        <v>67.27</v>
+        <v>83.29</v>
       </c>
       <c r="G28" s="2">
-        <v>66.989999999999995</v>
+        <v>66.650000000000006</v>
       </c>
       <c r="H28" s="2">
-        <v>67.27</v>
+        <v>83.29</v>
       </c>
       <c r="I28" s="2">
-        <v>78</v>
+        <v>77.77</v>
       </c>
       <c r="J28" s="2">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="K28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L28" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L28" xr:uid="{30144AD4-F371-48B7-B81D-C1548C034AB9}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="KITS19"/>
+        <filter val="MSD"/>
+        <filter val="SLIVER"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="SegResNet"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:L28">
+      <sortCondition ref="B1:B28"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L28">
     <sortCondition ref="A2:A28"/>
     <sortCondition ref="B2:B28"/>
     <sortCondition ref="C2:C28"/>
   </sortState>
-  <mergeCells count="12">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A8:A25"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B17:B19"/>
-  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="top10" dxfId="5" priority="1" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:I1048576">
+    <cfRule type="top10" dxfId="4" priority="6" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="top10" dxfId="3" priority="2" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="top10" dxfId="2" priority="3" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="top10" dxfId="1" priority="4" rank="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="top10" dxfId="0" priority="5" rank="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4275,10 +4714,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="11"/>
       <c r="C2" t="s">
         <v>8</v>
       </c>
@@ -4293,8 +4732,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
       <c r="C3" t="s">
         <v>30</v>
       </c>
@@ -4309,8 +4748,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
       <c r="C4" t="s">
         <v>40</v>
       </c>
@@ -4325,10 +4764,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
@@ -4345,8 +4784,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
       <c r="C6" t="s">
         <v>30</v>
       </c>
@@ -4361,8 +4800,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" t="s">
         <v>40</v>
       </c>
@@ -4377,10 +4816,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
@@ -4397,8 +4836,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" t="s">
         <v>30</v>
       </c>
@@ -4413,8 +4852,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
       <c r="C10" t="s">
         <v>40</v>
       </c>
@@ -4429,8 +4868,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
@@ -4447,8 +4886,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
       <c r="C12" t="s">
         <v>30</v>
       </c>
@@ -4463,8 +4902,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
       <c r="C13" t="s">
         <v>40</v>
       </c>
@@ -4479,8 +4918,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
@@ -4497,8 +4936,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
       <c r="C15" t="s">
         <v>30</v>
       </c>
@@ -4513,8 +4952,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
       <c r="C16" t="s">
         <v>40</v>
       </c>
@@ -4529,8 +4968,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
@@ -4547,8 +4986,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
       <c r="C18" t="s">
         <v>30</v>
       </c>
@@ -4563,8 +5002,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
       <c r="C19" t="s">
         <v>40</v>
       </c>
@@ -4579,8 +5018,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C20" t="s">
@@ -4597,8 +5036,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
       <c r="C21" t="s">
         <v>30</v>
       </c>
@@ -4613,8 +5052,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
       <c r="C22" t="s">
         <v>40</v>
       </c>
@@ -4629,8 +5068,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C23" t="s">
@@ -4647,8 +5086,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
       <c r="C24" t="s">
         <v>30</v>
       </c>
@@ -4663,8 +5102,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
       <c r="C25" t="s">
         <v>40</v>
       </c>
@@ -4679,10 +5118,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C26" t="s">
@@ -4699,8 +5138,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
       <c r="C27" t="s">
         <v>30</v>
       </c>
@@ -4715,8 +5154,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
       <c r="C28" t="s">
         <v>40</v>
       </c>
@@ -4747,4 +5186,1123 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF13E729-7A5C-45B3-B89B-FF16D445AC69}">
+  <dimension ref="A2:Q42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="K2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="K3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="9"/>
+      <c r="N3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="10"/>
+      <c r="P3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
+        <v>77.430000000000007</v>
+      </c>
+      <c r="C5" s="2">
+        <v>77.37</v>
+      </c>
+      <c r="D5" s="2">
+        <v>96.71</v>
+      </c>
+      <c r="E5" s="2">
+        <v>97.21</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77.89</v>
+      </c>
+      <c r="G5" s="2">
+        <v>77.8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="2">
+        <v>99.588009595870972</v>
+      </c>
+      <c r="M5" s="2">
+        <v>97.440188744711492</v>
+      </c>
+      <c r="N5" s="2">
+        <v>98.833034515380859</v>
+      </c>
+      <c r="O5" s="2">
+        <v>96.114333281441347</v>
+      </c>
+      <c r="P5" s="2">
+        <v>80.323452115058899</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>78.410340017742584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>70.14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>70.16</v>
+      </c>
+      <c r="D6" s="2">
+        <v>99.64</v>
+      </c>
+      <c r="E6" s="2">
+        <v>99.63</v>
+      </c>
+      <c r="F6" s="2">
+        <v>99.83</v>
+      </c>
+      <c r="G6" s="2">
+        <v>99.74</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="2">
+        <v>99.509807676076889</v>
+      </c>
+      <c r="M6" s="2">
+        <v>99.405782421429961</v>
+      </c>
+      <c r="N6" s="2">
+        <v>97.224900871515274</v>
+      </c>
+      <c r="O6" s="2">
+        <v>99.338068564732879</v>
+      </c>
+      <c r="P6" s="2">
+        <v>79.837141931056976</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>78.374321262041718</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2">
+        <v>82.99</v>
+      </c>
+      <c r="C7" s="2">
+        <v>81.52</v>
+      </c>
+      <c r="D7" s="2">
+        <v>97.88</v>
+      </c>
+      <c r="E7" s="2">
+        <v>97.98</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.6</v>
+      </c>
+      <c r="G7" s="2">
+        <v>99.63</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="2">
+        <v>99.197131493860041</v>
+      </c>
+      <c r="M7" s="2">
+        <v>99.54045017560324</v>
+      </c>
+      <c r="N7" s="2">
+        <v>98.922951605694351</v>
+      </c>
+      <c r="O7" s="2">
+        <v>96.931352217992156</v>
+      </c>
+      <c r="P7" s="2">
+        <v>88.285174596408183</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>80.052255590756744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2">
+        <v>75.84</v>
+      </c>
+      <c r="C8" s="2">
+        <v>75.83</v>
+      </c>
+      <c r="D8" s="2">
+        <v>99.87</v>
+      </c>
+      <c r="E8" s="2">
+        <v>99.87</v>
+      </c>
+      <c r="F8" s="2">
+        <v>77.790000000000006</v>
+      </c>
+      <c r="G8" s="2">
+        <v>77.790000000000006</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="2">
+        <v>99.950135957736236</v>
+      </c>
+      <c r="M8" s="2">
+        <v>99.948998445119614</v>
+      </c>
+      <c r="N8" s="2">
+        <v>99.96948895546106</v>
+      </c>
+      <c r="O8" s="2">
+        <v>99.96923124178862</v>
+      </c>
+      <c r="P8" s="2">
+        <v>78.284532003677811</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>78.298159822439544</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2">
+        <v>71.790000000000006</v>
+      </c>
+      <c r="C9" s="2">
+        <v>71.5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>94.59</v>
+      </c>
+      <c r="E9" s="2">
+        <v>95.74</v>
+      </c>
+      <c r="F9" s="2">
+        <v>78.489999999999995</v>
+      </c>
+      <c r="G9" s="2">
+        <v>78.319999999999993</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="2">
+        <v>98.057573891821363</v>
+      </c>
+      <c r="M9" s="2">
+        <v>99.701233373747939</v>
+      </c>
+      <c r="N9" s="2">
+        <v>96.727768225329257</v>
+      </c>
+      <c r="O9" s="2">
+        <v>98.699307110574509</v>
+      </c>
+      <c r="P9" s="2">
+        <v>78.373995707148609</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>80.913830134603714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2">
+        <v>69.63</v>
+      </c>
+      <c r="C10" s="2">
+        <v>69.8</v>
+      </c>
+      <c r="D10" s="2">
+        <v>99.59</v>
+      </c>
+      <c r="E10" s="2">
+        <v>99.5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>61.46</v>
+      </c>
+      <c r="G10" s="2">
+        <v>61.69</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2">
+        <v>99.160295724868774</v>
+      </c>
+      <c r="M10" s="2">
+        <v>99.815227517059867</v>
+      </c>
+      <c r="N10" s="2">
+        <v>99.341542273759842</v>
+      </c>
+      <c r="O10" s="2">
+        <v>99.581754988148091</v>
+      </c>
+      <c r="P10" s="2">
+        <v>78.210671246051788</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>79.903364039602735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
+        <v>77.680000000000007</v>
+      </c>
+      <c r="C11" s="2">
+        <v>77.64</v>
+      </c>
+      <c r="D11" s="2">
+        <v>99.96</v>
+      </c>
+      <c r="E11" s="2">
+        <v>99.89</v>
+      </c>
+      <c r="F11" s="2">
+        <v>81.62</v>
+      </c>
+      <c r="G11" s="2">
+        <v>81.94</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="2">
+        <v>99.647028923034668</v>
+      </c>
+      <c r="M11" s="2">
+        <v>99.241997467146987</v>
+      </c>
+      <c r="N11" s="2">
+        <v>97.905152797698975</v>
+      </c>
+      <c r="O11" s="2">
+        <v>98.9795669582155</v>
+      </c>
+      <c r="P11" s="2">
+        <v>80.036463737487793</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>88.083321783277725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2">
+        <v>74.989999999999995</v>
+      </c>
+      <c r="C12" s="2">
+        <v>74.989999999999995</v>
+      </c>
+      <c r="D12" s="2">
+        <v>99.85</v>
+      </c>
+      <c r="E12" s="2">
+        <v>99.86</v>
+      </c>
+      <c r="F12" s="2">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="G12" s="2">
+        <v>77.77</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="2">
+        <v>99.829206934997018</v>
+      </c>
+      <c r="M12" s="2">
+        <v>99.595714904166556</v>
+      </c>
+      <c r="N12" s="2">
+        <v>99.478502465145922</v>
+      </c>
+      <c r="O12" s="2">
+        <v>98.878433414407681</v>
+      </c>
+      <c r="P12" s="2">
+        <v>79.955087868230677</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>80.289389152784608</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="K19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+    </row>
+    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="O20" s="18"/>
+      <c r="P20" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2">
+        <f t="shared" ref="B22:G22" si="0">L5-B5</f>
+        <v>22.158009595870965</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="0"/>
+        <v>20.070188744711487</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>2.1230345153808656</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.0956667185586468</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="0"/>
+        <v>2.4334521150588984</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.61034001774258684</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" s="13">
+        <v>77.37</v>
+      </c>
+      <c r="M22" s="13">
+        <v>97.44</v>
+      </c>
+      <c r="N22" s="13">
+        <v>97.21</v>
+      </c>
+      <c r="O22" s="13">
+        <v>96.11</v>
+      </c>
+      <c r="P22" s="13">
+        <v>77.8</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>78.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2">
+        <f t="shared" ref="B23:B29" si="1">L6-B6</f>
+        <v>29.369807676076888</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" ref="C23:C29" si="2">M6-C6</f>
+        <v>29.245782421429965</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" ref="D23:D29" si="3">N6-D6</f>
+        <v>-2.4150991284847265</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" ref="E23:E29" si="4">O6-E6</f>
+        <v>-0.29193143526711651</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" ref="F23:F29" si="5">P6-F6</f>
+        <v>-19.992858068943022</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" ref="G23:G29" si="6">Q6-G6</f>
+        <v>-21.365678737958277</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="13">
+        <v>70.16</v>
+      </c>
+      <c r="M23" s="13">
+        <v>99.41</v>
+      </c>
+      <c r="N23" s="13">
+        <v>99.63</v>
+      </c>
+      <c r="O23" s="13">
+        <v>99.34</v>
+      </c>
+      <c r="P23" s="13">
+        <v>99.74</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>78.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>16.207131493860047</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="2"/>
+        <v>18.020450175603244</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="3"/>
+        <v>1.0429516056943555</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.0486477820078477</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="5"/>
+        <v>-11.314825403591811</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="6"/>
+        <v>-19.577744409243252</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="13">
+        <v>81.52</v>
+      </c>
+      <c r="M24" s="13">
+        <v>99.54</v>
+      </c>
+      <c r="N24" s="13">
+        <v>97.98</v>
+      </c>
+      <c r="O24" s="13">
+        <v>96.93</v>
+      </c>
+      <c r="P24" s="13">
+        <v>99.63</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>80.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="1"/>
+        <v>24.110135957736233</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="2"/>
+        <v>24.118998445119615</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="3"/>
+        <v>9.9488955461055184E-2</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="4"/>
+        <v>9.9231241788615421E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="5"/>
+        <v>0.49453200367780425</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="6"/>
+        <v>0.50815982243953783</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="13">
+        <v>75.83</v>
+      </c>
+      <c r="M25" s="13">
+        <v>99.95</v>
+      </c>
+      <c r="N25" s="13">
+        <v>99.87</v>
+      </c>
+      <c r="O25" s="13">
+        <v>99.97</v>
+      </c>
+      <c r="P25" s="13">
+        <v>77.790000000000006</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>78.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2">
+        <f t="shared" si="1"/>
+        <v>26.267573891821357</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="2"/>
+        <v>28.201233373747939</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="3"/>
+        <v>2.1377682253292534</v>
+      </c>
+      <c r="E26" s="2">
+        <f t="shared" si="4"/>
+        <v>2.9593071105745139</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="5"/>
+        <v>-0.11600429285138603</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="6"/>
+        <v>2.5938301346037207</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="13">
+        <v>71.5</v>
+      </c>
+      <c r="M26" s="13">
+        <v>99.7</v>
+      </c>
+      <c r="N26" s="13">
+        <v>95.74</v>
+      </c>
+      <c r="O26" s="13">
+        <v>98.7</v>
+      </c>
+      <c r="P26" s="13">
+        <v>78.319999999999993</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>80.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2">
+        <f t="shared" si="1"/>
+        <v>29.530295724868779</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" si="2"/>
+        <v>30.01522751705987</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="3"/>
+        <v>-0.24845772624016149</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="4"/>
+        <v>8.1754988148091456E-2</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="5"/>
+        <v>16.750671246051787</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="6"/>
+        <v>18.213364039602737</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="13">
+        <v>69.8</v>
+      </c>
+      <c r="M27" s="13">
+        <v>99.82</v>
+      </c>
+      <c r="N27" s="13">
+        <v>99.5</v>
+      </c>
+      <c r="O27" s="13">
+        <v>99.58</v>
+      </c>
+      <c r="P27" s="13">
+        <v>61.69</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <f t="shared" si="1"/>
+        <v>21.967028923034661</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="2"/>
+        <v>21.601997467146987</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="3"/>
+        <v>-2.0548472023010191</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" si="4"/>
+        <v>-0.91043304178450057</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="5"/>
+        <v>-1.5835362625122116</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" si="6"/>
+        <v>6.1433217832777274</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="13">
+        <v>77.64</v>
+      </c>
+      <c r="M28" s="13">
+        <v>99.24</v>
+      </c>
+      <c r="N28" s="13">
+        <v>99.89</v>
+      </c>
+      <c r="O28" s="13">
+        <v>98.98</v>
+      </c>
+      <c r="P28" s="13">
+        <v>81.94</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>88.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <f t="shared" si="1"/>
+        <v>24.839206934997023</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="2"/>
+        <v>24.605714904166561</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="3"/>
+        <v>-0.37149753485407189</v>
+      </c>
+      <c r="E29" s="2">
+        <f t="shared" si="4"/>
+        <v>-0.98156658559231857</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="5"/>
+        <v>2.1950878682306723</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="6"/>
+        <v>2.519389152784612</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="13">
+        <v>74.989999999999995</v>
+      </c>
+      <c r="M29" s="13">
+        <v>99.6</v>
+      </c>
+      <c r="N29" s="13">
+        <v>99.86</v>
+      </c>
+      <c r="O29" s="13">
+        <v>98.88</v>
+      </c>
+      <c r="P29" s="13">
+        <v>77.77</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>80.290000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K33" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+    </row>
+    <row r="34" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K34" s="9"/>
+      <c r="L34" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K35" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="2">
+        <v>20.070188744711487</v>
+      </c>
+      <c r="M35" s="2">
+        <v>-1.0956667185586468</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0.61034001774258684</v>
+      </c>
+    </row>
+    <row r="36" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="2">
+        <v>29.245782421429965</v>
+      </c>
+      <c r="M36" s="2">
+        <v>-0.29193143526711651</v>
+      </c>
+      <c r="N36" s="2">
+        <v>-21.365678737958277</v>
+      </c>
+    </row>
+    <row r="37" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K37" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="2">
+        <v>18.020450175603244</v>
+      </c>
+      <c r="M37" s="2">
+        <v>-1.0486477820078477</v>
+      </c>
+      <c r="N37" s="2">
+        <v>-19.577744409243252</v>
+      </c>
+    </row>
+    <row r="38" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="2">
+        <v>24.118998445119615</v>
+      </c>
+      <c r="M38" s="2">
+        <v>9.9231241788615421E-2</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.50815982243953783</v>
+      </c>
+    </row>
+    <row r="39" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="2">
+        <v>28.201233373747939</v>
+      </c>
+      <c r="M39" s="2">
+        <v>2.9593071105745139</v>
+      </c>
+      <c r="N39" s="2">
+        <v>2.5938301346037207</v>
+      </c>
+    </row>
+    <row r="40" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="2">
+        <v>30.01522751705987</v>
+      </c>
+      <c r="M40" s="2">
+        <v>8.1754988148091456E-2</v>
+      </c>
+      <c r="N40" s="2">
+        <v>18.213364039602737</v>
+      </c>
+    </row>
+    <row r="41" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K41" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="2">
+        <v>21.601997467146987</v>
+      </c>
+      <c r="M41" s="2">
+        <v>-0.91043304178450057</v>
+      </c>
+      <c r="N41" s="2">
+        <v>6.1433217832777274</v>
+      </c>
+    </row>
+    <row r="42" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="2">
+        <v>24.605714904166561</v>
+      </c>
+      <c r="M42" s="2">
+        <v>-0.98156658559231857</v>
+      </c>
+      <c r="N42" s="2">
+        <v>2.519389152784612</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="K33:K34"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>